--- a/data/MT_PRIMARY4_1.xlsx
+++ b/data/MT_PRIMARY4_1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zerihuworkineh/Desktop/MT_MANUSCRIPT/MANUS1_MATLAB/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zerihuworkineh/Desktop/MT_MANUSCRIPT/MANUS1_MATLAB/NP_MT_ALL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C966CCCB-F3E6-CC4A-AA26-9335B45F2980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DF11BD-F10C-5442-82D0-E5E202971720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40" yWindow="760" windowWidth="26240" windowHeight="17840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="228">
   <si>
     <t>Activators</t>
   </si>
@@ -690,22 +690,6 @@
     <t>MitD</t>
   </si>
   <si>
-    <t>NutD,ROS</t>
-  </si>
-  <si>
-    <r>
-      <t>ERK-M,mTORC1,JNK,P38,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>NutD</t>
-    </r>
-  </si>
-  <si>
     <r>
       <t>Ca2+os,LKB1,</t>
     </r>
@@ -748,19 +732,6 @@
         <rFont val="Calibri (Body)"/>
       </rPr>
       <t>,ROS</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ROCK-E,Ca2+su,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>NutD,DRP1</t>
     </r>
   </si>
   <si>
@@ -851,6 +822,22 @@
       </rPr>
       <t>HIF-1α</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>ROCK-E,Ca2+su</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>,DRP1</t>
+    </r>
+  </si>
+  <si>
+    <t>ERK-M,mTORC1,JNK,P38</t>
   </si>
 </sst>
 </file>
@@ -1232,7 +1219,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D148"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1256,12 +1242,12 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>114</v>
@@ -1284,7 +1270,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>152</v>
       </c>
@@ -1298,7 +1284,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1312,12 +1298,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C6" t="s">
         <v>96</v>
@@ -1326,7 +1312,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>113</v>
       </c>
@@ -1340,7 +1326,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1348,13 +1334,13 @@
         <v>191</v>
       </c>
       <c r="C8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>203</v>
       </c>
@@ -1368,7 +1354,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>204</v>
       </c>
@@ -1382,7 +1368,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1396,7 +1382,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1410,7 +1396,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1424,7 +1410,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>101</v>
       </c>
@@ -1438,7 +1424,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -1452,7 +1438,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>132</v>
       </c>
@@ -1466,7 +1452,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>133</v>
       </c>
@@ -1480,7 +1466,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1494,7 +1480,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1508,7 +1494,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1522,7 +1508,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -1536,7 +1522,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -1550,7 +1536,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -1564,7 +1550,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -1578,7 +1564,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -1592,7 +1578,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>139</v>
       </c>
@@ -1606,7 +1592,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>16</v>
       </c>
@@ -1620,7 +1606,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -1634,12 +1620,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>114</v>
@@ -1648,7 +1634,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>157</v>
       </c>
@@ -1662,7 +1648,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>19</v>
       </c>
@@ -1676,7 +1662,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>20</v>
       </c>
@@ -1690,7 +1676,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>185</v>
       </c>
@@ -1704,7 +1690,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>110</v>
       </c>
@@ -1718,12 +1704,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>104</v>
       </c>
       <c r="B35" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C35" t="s">
         <v>114</v>
@@ -1732,12 +1718,12 @@
         <v>104</v>
       </c>
     </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C36" t="s">
         <v>114</v>
@@ -1746,7 +1732,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>24</v>
       </c>
@@ -1760,7 +1746,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -1774,7 +1760,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>26</v>
       </c>
@@ -1788,7 +1774,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>27</v>
       </c>
@@ -1802,7 +1788,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>28</v>
       </c>
@@ -1816,7 +1802,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -1830,12 +1816,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>30</v>
       </c>
       <c r="B43" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C43" t="s">
         <v>179</v>
@@ -1844,7 +1830,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>31</v>
       </c>
@@ -1858,7 +1844,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>32</v>
       </c>
@@ -1872,7 +1858,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>33</v>
       </c>
@@ -1886,7 +1872,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>34</v>
       </c>
@@ -1900,21 +1886,21 @@
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+    <row r="48" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B48" t="s">
-        <v>215</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="B48" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>36</v>
       </c>
@@ -1928,7 +1914,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>37</v>
       </c>
@@ -1942,7 +1928,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>38</v>
       </c>
@@ -1956,7 +1942,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>39</v>
       </c>
@@ -1970,7 +1956,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>159</v>
       </c>
@@ -1984,7 +1970,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>153</v>
       </c>
@@ -1998,7 +1984,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>40</v>
       </c>
@@ -2012,7 +1998,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>41</v>
       </c>
@@ -2026,7 +2012,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>115</v>
       </c>
@@ -2040,7 +2026,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>42</v>
       </c>
@@ -2054,7 +2040,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>43</v>
       </c>
@@ -2068,7 +2054,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -2082,12 +2068,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>109</v>
       </c>
       <c r="B61" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C61" t="s">
         <v>21</v>
@@ -2096,7 +2082,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>44</v>
       </c>
@@ -2110,7 +2096,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>45</v>
       </c>
@@ -2124,7 +2110,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>46</v>
       </c>
@@ -2138,7 +2124,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>47</v>
       </c>
@@ -2152,7 +2138,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>118</v>
       </c>
@@ -2166,7 +2152,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>48</v>
       </c>
@@ -2180,7 +2166,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>49</v>
       </c>
@@ -2194,7 +2180,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>119</v>
       </c>
@@ -2208,7 +2194,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>120</v>
       </c>
@@ -2222,7 +2208,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>50</v>
       </c>
@@ -2236,7 +2222,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>51</v>
       </c>
@@ -2250,7 +2236,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>52</v>
       </c>
@@ -2264,7 +2250,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>53</v>
       </c>
@@ -2278,7 +2264,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>54</v>
       </c>
@@ -2292,7 +2278,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>55</v>
       </c>
@@ -2306,7 +2292,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>96</v>
       </c>
@@ -2320,7 +2306,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>97</v>
       </c>
@@ -2334,12 +2320,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>56</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C79" t="s">
         <v>44</v>
@@ -2348,7 +2334,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>57</v>
       </c>
@@ -2362,7 +2348,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>58</v>
       </c>
@@ -2376,7 +2362,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>59</v>
       </c>
@@ -2390,12 +2376,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>60</v>
       </c>
       <c r="B83" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C83" t="s">
         <v>114</v>
@@ -2404,7 +2390,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>61</v>
       </c>
@@ -2418,7 +2404,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>151</v>
       </c>
@@ -2432,7 +2418,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>62</v>
       </c>
@@ -2446,7 +2432,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>63</v>
       </c>
@@ -2460,7 +2446,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>146</v>
       </c>
@@ -2474,7 +2460,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>150</v>
       </c>
@@ -2488,7 +2474,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>64</v>
       </c>
@@ -2502,7 +2488,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>65</v>
       </c>
@@ -2516,7 +2502,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>66</v>
       </c>
@@ -2530,7 +2516,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>67</v>
       </c>
@@ -2544,7 +2530,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="94" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>186</v>
       </c>
@@ -2558,7 +2544,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="95" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>187</v>
       </c>
@@ -2572,7 +2558,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>68</v>
       </c>
@@ -2586,7 +2572,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>111</v>
       </c>
@@ -2600,7 +2586,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>192</v>
       </c>
@@ -2614,7 +2600,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>193</v>
       </c>
@@ -2628,7 +2614,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2642,7 +2628,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>107</v>
       </c>
@@ -2656,12 +2642,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>69</v>
       </c>
       <c r="B102" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C102" t="s">
         <v>114</v>
@@ -2670,7 +2656,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>194</v>
       </c>
@@ -2684,7 +2670,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>195</v>
       </c>
@@ -2698,7 +2684,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>70</v>
       </c>
@@ -2712,7 +2698,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>71</v>
       </c>
@@ -2726,7 +2712,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>72</v>
       </c>
@@ -2740,7 +2726,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>73</v>
       </c>
@@ -2754,7 +2740,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>149</v>
       </c>
@@ -2768,7 +2754,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>78</v>
       </c>
@@ -2782,7 +2768,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>79</v>
       </c>
@@ -2796,7 +2782,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>74</v>
       </c>
@@ -2810,7 +2796,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>75</v>
       </c>
@@ -2824,12 +2810,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>76</v>
       </c>
       <c r="B114" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C114" t="s">
         <v>82</v>
@@ -2838,7 +2824,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>161</v>
       </c>
@@ -2852,7 +2838,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>77</v>
       </c>
@@ -2866,7 +2852,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>80</v>
       </c>
@@ -2880,7 +2866,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>81</v>
       </c>
@@ -2894,7 +2880,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>82</v>
       </c>
@@ -2908,7 +2894,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>83</v>
       </c>
@@ -2922,7 +2908,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>102</v>
       </c>
@@ -2936,7 +2922,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>103</v>
       </c>
@@ -2950,7 +2936,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>84</v>
       </c>
@@ -2964,7 +2950,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>85</v>
       </c>
@@ -2978,7 +2964,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>86</v>
       </c>
@@ -2992,7 +2978,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>144</v>
       </c>
@@ -3006,12 +2992,12 @@
         <v>144</v>
       </c>
     </row>
-    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>108</v>
       </c>
       <c r="B127" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>5</v>
@@ -3020,7 +3006,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>87</v>
       </c>
@@ -3034,7 +3020,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>89</v>
       </c>
@@ -3048,7 +3034,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>88</v>
       </c>
@@ -3062,7 +3048,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>90</v>
       </c>
@@ -3076,7 +3062,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>91</v>
       </c>
@@ -3090,7 +3076,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>147</v>
       </c>
@@ -3104,7 +3090,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>92</v>
       </c>
@@ -3118,7 +3104,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>93</v>
       </c>
@@ -3132,7 +3118,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>94</v>
       </c>
@@ -3146,7 +3132,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>136</v>
       </c>
@@ -3160,7 +3146,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>137</v>
       </c>
@@ -3174,7 +3160,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>98</v>
       </c>
@@ -3188,7 +3174,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>145</v>
       </c>
@@ -3202,7 +3188,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>99</v>
       </c>
@@ -3216,7 +3202,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>106</v>
       </c>
@@ -3230,7 +3216,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>105</v>
       </c>
@@ -3244,7 +3230,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="144" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
         <v>188</v>
       </c>
@@ -3258,7 +3244,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="145" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
         <v>189</v>
       </c>
@@ -3272,7 +3258,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>210</v>
       </c>
@@ -3286,12 +3272,12 @@
         <v>210</v>
       </c>
     </row>
-    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>212</v>
       </c>
       <c r="B147" t="s">
-        <v>210</v>
+        <v>114</v>
       </c>
       <c r="C147" t="s">
         <v>114</v>
@@ -3300,28 +3286,22 @@
         <v>212</v>
       </c>
     </row>
-    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A148" t="s">
+    <row r="148" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B148" t="s">
-        <v>214</v>
+      <c r="B148" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D148" t="s">
+      <c r="D148" s="2" t="s">
         <v>213</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C148" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="ADAMTS4/5"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:C148" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D141">
     <sortCondition ref="A2:A141"/>
   </sortState>

--- a/data/MT_PRIMARY4_1.xlsx
+++ b/data/MT_PRIMARY4_1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zerihuworkineh/Desktop/MT_MANUSCRIPT/MANUS1_MATLAB/NP_MT_ALL/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zerihuworkineh/Desktop/MT_MANUSCRIPT/MANUS1_MATLAB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DF11BD-F10C-5442-82D0-E5E202971720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C966CCCB-F3E6-CC4A-AA26-9335B45F2980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40" yWindow="760" windowWidth="26240" windowHeight="17840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="229">
   <si>
     <t>Activators</t>
   </si>
@@ -690,6 +690,22 @@
     <t>MitD</t>
   </si>
   <si>
+    <t>NutD,ROS</t>
+  </si>
+  <si>
+    <r>
+      <t>ERK-M,mTORC1,JNK,P38,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>NutD</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t>Ca2+os,LKB1,</t>
     </r>
@@ -732,6 +748,19 @@
         <rFont val="Calibri (Body)"/>
       </rPr>
       <t>,ROS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ROCK-E,Ca2+su,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>NutD,DRP1</t>
     </r>
   </si>
   <si>
@@ -822,22 +851,6 @@
       </rPr>
       <t>HIF-1α</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>ROCK-E,Ca2+su</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>,DRP1</t>
-    </r>
-  </si>
-  <si>
-    <t>ERK-M,mTORC1,JNK,P38</t>
   </si>
 </sst>
 </file>
@@ -1219,6 +1232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D148"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1242,12 +1256,12 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>114</v>
@@ -1270,7 +1284,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>152</v>
       </c>
@@ -1284,7 +1298,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1298,12 +1312,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C6" t="s">
         <v>96</v>
@@ -1312,7 +1326,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>113</v>
       </c>
@@ -1326,7 +1340,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1334,13 +1348,13 @@
         <v>191</v>
       </c>
       <c r="C8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>203</v>
       </c>
@@ -1354,7 +1368,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>204</v>
       </c>
@@ -1368,7 +1382,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1382,7 +1396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1396,7 +1410,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1410,7 +1424,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>101</v>
       </c>
@@ -1424,7 +1438,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -1438,7 +1452,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>132</v>
       </c>
@@ -1452,7 +1466,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>133</v>
       </c>
@@ -1466,7 +1480,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1480,7 +1494,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1494,7 +1508,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1508,7 +1522,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -1522,7 +1536,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -1536,7 +1550,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -1550,7 +1564,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -1564,7 +1578,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -1578,7 +1592,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>139</v>
       </c>
@@ -1592,7 +1606,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>16</v>
       </c>
@@ -1606,7 +1620,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -1620,12 +1634,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>114</v>
@@ -1634,7 +1648,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>157</v>
       </c>
@@ -1648,7 +1662,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>19</v>
       </c>
@@ -1662,7 +1676,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>20</v>
       </c>
@@ -1676,7 +1690,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>185</v>
       </c>
@@ -1690,7 +1704,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>110</v>
       </c>
@@ -1704,12 +1718,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>104</v>
       </c>
       <c r="B35" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C35" t="s">
         <v>114</v>
@@ -1718,12 +1732,12 @@
         <v>104</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C36" t="s">
         <v>114</v>
@@ -1732,7 +1746,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>24</v>
       </c>
@@ -1746,7 +1760,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -1760,7 +1774,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>26</v>
       </c>
@@ -1774,7 +1788,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>27</v>
       </c>
@@ -1788,7 +1802,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>28</v>
       </c>
@@ -1802,7 +1816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -1816,12 +1830,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>30</v>
       </c>
       <c r="B43" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C43" t="s">
         <v>179</v>
@@ -1830,7 +1844,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>31</v>
       </c>
@@ -1844,7 +1858,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>32</v>
       </c>
@@ -1858,7 +1872,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>33</v>
       </c>
@@ -1872,7 +1886,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>34</v>
       </c>
@@ -1886,21 +1900,21 @@
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
         <v>35</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="C48" s="2" t="s">
+      <c r="B48" t="s">
+        <v>215</v>
+      </c>
+      <c r="C48" t="s">
         <v>34</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>36</v>
       </c>
@@ -1914,7 +1928,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>37</v>
       </c>
@@ -1928,7 +1942,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>38</v>
       </c>
@@ -1942,7 +1956,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>39</v>
       </c>
@@ -1956,7 +1970,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>159</v>
       </c>
@@ -1970,7 +1984,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>153</v>
       </c>
@@ -1984,7 +1998,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>40</v>
       </c>
@@ -1998,7 +2012,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>41</v>
       </c>
@@ -2012,7 +2026,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>115</v>
       </c>
@@ -2026,7 +2040,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>42</v>
       </c>
@@ -2040,7 +2054,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>43</v>
       </c>
@@ -2054,7 +2068,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -2068,12 +2082,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>109</v>
       </c>
       <c r="B61" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C61" t="s">
         <v>21</v>
@@ -2082,7 +2096,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>44</v>
       </c>
@@ -2096,7 +2110,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>45</v>
       </c>
@@ -2110,7 +2124,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>46</v>
       </c>
@@ -2124,7 +2138,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>47</v>
       </c>
@@ -2138,7 +2152,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>118</v>
       </c>
@@ -2152,7 +2166,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>48</v>
       </c>
@@ -2166,7 +2180,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>49</v>
       </c>
@@ -2180,7 +2194,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>119</v>
       </c>
@@ -2194,7 +2208,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>120</v>
       </c>
@@ -2208,7 +2222,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>50</v>
       </c>
@@ -2222,7 +2236,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>51</v>
       </c>
@@ -2236,7 +2250,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>52</v>
       </c>
@@ -2250,7 +2264,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>53</v>
       </c>
@@ -2264,7 +2278,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>54</v>
       </c>
@@ -2278,7 +2292,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>55</v>
       </c>
@@ -2292,7 +2306,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>96</v>
       </c>
@@ -2306,7 +2320,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>97</v>
       </c>
@@ -2320,12 +2334,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>56</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C79" t="s">
         <v>44</v>
@@ -2334,7 +2348,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>57</v>
       </c>
@@ -2348,7 +2362,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>58</v>
       </c>
@@ -2362,7 +2376,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>59</v>
       </c>
@@ -2376,12 +2390,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>60</v>
       </c>
       <c r="B83" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C83" t="s">
         <v>114</v>
@@ -2390,7 +2404,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>61</v>
       </c>
@@ -2404,7 +2418,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>151</v>
       </c>
@@ -2418,7 +2432,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>62</v>
       </c>
@@ -2432,7 +2446,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>63</v>
       </c>
@@ -2446,7 +2460,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>146</v>
       </c>
@@ -2460,7 +2474,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>150</v>
       </c>
@@ -2474,7 +2488,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>64</v>
       </c>
@@ -2488,7 +2502,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>65</v>
       </c>
@@ -2502,7 +2516,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>66</v>
       </c>
@@ -2516,7 +2530,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>67</v>
       </c>
@@ -2530,7 +2544,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="94" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>186</v>
       </c>
@@ -2544,7 +2558,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="95" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>187</v>
       </c>
@@ -2558,7 +2572,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>68</v>
       </c>
@@ -2572,7 +2586,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>111</v>
       </c>
@@ -2586,7 +2600,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>192</v>
       </c>
@@ -2600,7 +2614,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>193</v>
       </c>
@@ -2614,7 +2628,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2628,7 +2642,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>107</v>
       </c>
@@ -2642,12 +2656,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>69</v>
       </c>
       <c r="B102" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C102" t="s">
         <v>114</v>
@@ -2656,7 +2670,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>194</v>
       </c>
@@ -2670,7 +2684,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>195</v>
       </c>
@@ -2684,7 +2698,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>70</v>
       </c>
@@ -2698,7 +2712,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>71</v>
       </c>
@@ -2712,7 +2726,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>72</v>
       </c>
@@ -2726,7 +2740,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>73</v>
       </c>
@@ -2740,7 +2754,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>149</v>
       </c>
@@ -2754,7 +2768,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>78</v>
       </c>
@@ -2768,7 +2782,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>79</v>
       </c>
@@ -2782,7 +2796,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>74</v>
       </c>
@@ -2796,7 +2810,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>75</v>
       </c>
@@ -2810,12 +2824,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>76</v>
       </c>
       <c r="B114" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C114" t="s">
         <v>82</v>
@@ -2824,7 +2838,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>161</v>
       </c>
@@ -2838,7 +2852,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>77</v>
       </c>
@@ -2852,7 +2866,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>80</v>
       </c>
@@ -2866,7 +2880,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>81</v>
       </c>
@@ -2880,7 +2894,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>82</v>
       </c>
@@ -2894,7 +2908,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>83</v>
       </c>
@@ -2908,7 +2922,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>102</v>
       </c>
@@ -2922,7 +2936,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>103</v>
       </c>
@@ -2936,7 +2950,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>84</v>
       </c>
@@ -2950,7 +2964,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>85</v>
       </c>
@@ -2964,7 +2978,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>86</v>
       </c>
@@ -2978,7 +2992,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>144</v>
       </c>
@@ -2992,12 +3006,12 @@
         <v>144</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>108</v>
       </c>
       <c r="B127" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>5</v>
@@ -3006,7 +3020,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>87</v>
       </c>
@@ -3020,7 +3034,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>89</v>
       </c>
@@ -3034,7 +3048,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>88</v>
       </c>
@@ -3048,7 +3062,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>90</v>
       </c>
@@ -3062,7 +3076,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>91</v>
       </c>
@@ -3076,7 +3090,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>147</v>
       </c>
@@ -3090,7 +3104,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>92</v>
       </c>
@@ -3104,7 +3118,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>93</v>
       </c>
@@ -3118,7 +3132,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>94</v>
       </c>
@@ -3132,7 +3146,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>136</v>
       </c>
@@ -3146,7 +3160,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>137</v>
       </c>
@@ -3160,7 +3174,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>98</v>
       </c>
@@ -3174,7 +3188,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>145</v>
       </c>
@@ -3188,7 +3202,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>99</v>
       </c>
@@ -3202,7 +3216,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>106</v>
       </c>
@@ -3216,7 +3230,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>105</v>
       </c>
@@ -3230,7 +3244,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="144" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
         <v>188</v>
       </c>
@@ -3244,7 +3258,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="145" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
         <v>189</v>
       </c>
@@ -3258,7 +3272,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>210</v>
       </c>
@@ -3272,12 +3286,12 @@
         <v>210</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>212</v>
       </c>
       <c r="B147" t="s">
-        <v>114</v>
+        <v>210</v>
       </c>
       <c r="C147" t="s">
         <v>114</v>
@@ -3286,22 +3300,28 @@
         <v>212</v>
       </c>
     </row>
-    <row r="148" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="2" t="s">
+    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
         <v>213</v>
       </c>
-      <c r="B148" s="2" t="s">
-        <v>76</v>
+      <c r="B148" t="s">
+        <v>214</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D148" s="2" t="s">
+      <c r="D148" t="s">
         <v>213</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C148" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:C148" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="ADAMTS4/5"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D141">
     <sortCondition ref="A2:A141"/>
   </sortState>
